--- a/financial_advisor_forms/013_personal_finance_organizer--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/013_personal_finance_organizer--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>income_earnings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>Monthly income</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>expenses</t>
+          <t>expenses_spendings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>expenses</t>
+          <t>Monthly expenses</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>savings_goals</t>
+          <t>savings_targets</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>savings_goals</t>
+          <t>Monthly savings</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>savings_priority</t>
+          <t>save_priority</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>savings_priority</t>
+          <t>Saving priority</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>Income amount</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>expenses</t>
+          <t>expenses_amount</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>expenses</t>
+          <t>Expenses amount</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>savings_goals</t>
+          <t>savings_goal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>savings_goals</t>
+          <t>Savings goal</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>savings_priority</t>
+          <t>save_phone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>savings_priority</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>savings_priority_important</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Savings priority importance</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,182 +722,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>Email address</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>money_priority</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>money_priority</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>income</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>income</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>expenses</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>expenses</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>savings_goals</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>savings_goals</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>savings_priority</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>savings_priority</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -914,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -942,136 +781,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>savings_priority_choices</t>
+          <t>save_priority_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>savings_priority_choices</t>
+          <t>save_priority_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>savings_priority_choices</t>
+          <t>save_priority_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>savings_priority_choices</t>
+          <t>savings_priority_important_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>money_priority_choices</t>
+          <t>savings_priority_important_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>money_priority_choices</t>
+          <t>savings_priority_important_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>savings_priority_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>savings_priority_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
